--- a/Tendo_Monitoring_data/20260330_New_Tendo_Funnel_scorecard2_0_peso_dec25.xlsx
+++ b/Tendo_Monitoring_data/20260330_New_Tendo_Funnel_scorecard2_0_peso_dec25.xlsx
@@ -455,16 +455,16 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>3174333.5</v>
+        <v>3383583.5</v>
       </c>
       <c r="D3">
-        <v>1128698.139</v>
+        <v>1264513.098</v>
       </c>
       <c r="E3">
-        <v>1032891.722</v>
+        <v>1153953.748</v>
       </c>
       <c r="F3">
-        <v>764730.91</v>
+        <v>885792.936</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -475,7 +475,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>2178571</v>
+        <v>2216971</v>
       </c>
       <c r="D4">
         <v>767525.397</v>
@@ -495,16 +495,16 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>2382031</v>
+        <v>2500398</v>
       </c>
       <c r="D5">
-        <v>942562.473</v>
+        <v>1006134.671</v>
       </c>
       <c r="E5">
-        <v>950550.112</v>
+        <v>1030227.406</v>
       </c>
       <c r="F5">
-        <v>679417.8149999999</v>
+        <v>759095.1090000001</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -515,16 +515,16 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>1404889</v>
+        <v>1652221</v>
       </c>
       <c r="D6">
-        <v>428865.799</v>
+        <v>468407.201</v>
       </c>
       <c r="E6">
-        <v>369538.541</v>
+        <v>418429.77</v>
       </c>
       <c r="F6">
-        <v>300085.755</v>
+        <v>348976.984</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="C8">
-        <v>690136</v>
+        <v>725192</v>
       </c>
       <c r="D8">
         <v>128042.459</v>
       </c>
       <c r="E8">
-        <v>132374.078</v>
+        <v>153979.9</v>
       </c>
       <c r="F8">
-        <v>102179.732</v>
+        <v>123785.554</v>
       </c>
     </row>
   </sheetData>
